--- a/data/trending_integrated_20261006_14.xlsx
+++ b/data/trending_integrated_20261006_14.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7150</v>
+        <v>13010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+30.00%</t>
+          <t>'+29.97%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>121</v>
+        <v>242</v>
       </c>
       <c r="H2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5500</v>
+        <v>10010</v>
       </c>
       <c r="K2" t="n">
-        <v>6170</v>
+        <v>10530</v>
       </c>
       <c r="L2" t="n">
-        <v>7150</v>
+        <v>13010</v>
       </c>
       <c r="M2" t="n">
-        <v>5920</v>
+        <v>10110</v>
       </c>
       <c r="N2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>104831415125</v>
+        <v>52848914990</v>
       </c>
       <c r="P2" t="n">
-        <v>11370</v>
+        <v>22250</v>
       </c>
       <c r="Q2" t="n">
-        <v>3300</v>
+        <v>6000</v>
       </c>
       <c r="R2" t="n">
-        <v>60000</v>
+        <v>553000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-34000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>우리은행 해킹 방어 관련 티오리 협력 언급. 3분기 흑자 전환 및 보안주 동반 상승 기대.</t>
+          <t>HLB와의 연관성 및 유증 물량 소화 완료에 따른 주가 상승 기대감. FDA 승인 모멘텀 주목.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['보안주', '양자암호', '흑자']</t>
+          <t>['HLB', '유증', 'FDA']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,77 +648,77 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13010</v>
+        <v>7075</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+29.97%</t>
+          <t>'+28.64%</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E3" t="n">
+        <v>107</v>
+      </c>
+      <c r="F3" t="n">
+        <v>71</v>
+      </c>
+      <c r="G3" t="n">
+        <v>126</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>5500</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6170</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7150</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5920</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>110265535010</v>
+      </c>
+      <c r="P3" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R3" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>86</v>
-      </c>
-      <c r="F3" t="n">
-        <v>66</v>
-      </c>
-      <c r="G3" t="n">
-        <v>241</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>10010</v>
-      </c>
-      <c r="K3" t="n">
-        <v>10530</v>
-      </c>
-      <c r="L3" t="n">
-        <v>13010</v>
-      </c>
-      <c r="M3" t="n">
-        <v>10110</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>52837205990</v>
-      </c>
-      <c r="P3" t="n">
-        <v>22250</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>553000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-34000</v>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB와의 연관성 및 유증 물량 소화 완료에 따른 주가 상승 기대감. FDA 승인 모멘텀 주목.</t>
+          <t>우리은행 해킹 방어 관련 티오리 협력 언급. 3분기 흑자 전환 및 보안주 동반 상승 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['HLB', '유증', 'FDA']</t>
+          <t>['보안주', '양자암호', '흑자']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18080</v>
+        <v>17880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.71%</t>
+          <t>'+16.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H4" t="n">
         <v>2.17</v>
@@ -794,7 +794,7 @@
         <v>1.37</v>
       </c>
       <c r="O4" t="n">
-        <v>103432718840</v>
+        <v>104706575075</v>
       </c>
       <c r="P4" t="n">
         <v>38400</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46450</v>
+        <v>46900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.83%</t>
+          <t>'+15.95%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>770</v>
+        <v>784</v>
       </c>
       <c r="F5" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G5" t="n">
-        <v>4618</v>
+        <v>4682</v>
       </c>
       <c r="H5" t="n">
         <v>14.1</v>
@@ -886,7 +886,7 @@
         <v>14.11</v>
       </c>
       <c r="O5" t="n">
-        <v>246208172300</v>
+        <v>248611245750</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -946,13 +946,13 @@
         <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H6" t="n">
         <v>1.4</v>
@@ -978,7 +978,7 @@
         <v>1.02</v>
       </c>
       <c r="O6" t="n">
-        <v>136666183934</v>
+        <v>137151862322</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3190</v>
+        <v>3130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+12.13%</t>
+          <t>'+10.02%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H7" t="n">
         <v>1.82</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>50451175326</v>
+        <v>51428050602</v>
       </c>
       <c r="P7" t="n">
         <v>4810</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20850</v>
+        <v>20500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+10.96%</t>
+          <t>'+9.10%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>78</v>
       </c>
       <c r="G8" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
@@ -1162,7 +1162,7 @@
         <v>0.83</v>
       </c>
       <c r="O8" t="n">
-        <v>140779619465</v>
+        <v>142594911290</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>금융권 AI 공격 관련 보안주 동반 상승 전망. 양자 보안 기술 기반 주가 상승 기대.</t>
+          <t>은행권 보안 이슈와 연관된 보안주로서 연말 상승 기대감 표출. 긍정적 상승 징조 및 양자 보안 관련 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', '양자보안', 'AI']</t>
+          <t>['보안주', '양자 보안', '상승 기대']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.69%</t>
+          <t>'+7.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.17</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="H9" t="n">
         <v>1.09</v>
@@ -1254,7 +1254,7 @@
         <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>20023038652</v>
+        <v>20082380898</v>
       </c>
       <c r="P9" t="n">
         <v>2970</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18400</v>
+        <v>18430</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.37%</t>
+          <t>'+3.54%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>79</v>
       </c>
       <c r="G10" t="n">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H10" t="n">
         <v>3.81</v>
@@ -1346,7 +1346,7 @@
         <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>210130266625</v>
+        <v>212210875780</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1406,13 +1406,13 @@
         <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H11" t="n">
         <v>9.390000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>57331588500</v>
+        <v>58171706540</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15210</v>
+        <v>15360</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.91%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.14</v>
       </c>
       <c r="E12" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="H12" t="n">
         <v>0.32</v>
@@ -1530,7 +1530,7 @@
         <v>0.18</v>
       </c>
       <c r="O12" t="n">
-        <v>68693316850</v>
+        <v>69713846510</v>
       </c>
       <c r="P12" t="n">
         <v>29750</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>기타법인의 대규모 자사주 매집 확인. 향후 주가 상승에 대한 기대감과 함께 변동성 가능성 언급.</t>
+          <t>기타법인 자사주 매집에 대한 의문 제기 및 초저평가 논의. 주가 상승에 대한 기대와 함께 단기적인 움직임에 대한 관망세.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주 매집', '기타법인', '빅웨이브']</t>
+          <t>['자사주 매집', '초저평가', '수급']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,10 +1590,10 @@
         <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" t="n">
         <v>304</v>
@@ -1622,7 +1622,7 @@
         <v>27.73</v>
       </c>
       <c r="O13" t="n">
-        <v>36686286775</v>
+        <v>37142476385</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>270500</v>
+        <v>271000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.99%</t>
+          <t>'-1.81%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G14" t="n">
-        <v>1553</v>
+        <v>1523</v>
       </c>
       <c r="H14" t="n">
         <v>46.41</v>
@@ -1714,7 +1714,7 @@
         <v>46.41</v>
       </c>
       <c r="O14" t="n">
-        <v>2398158699750</v>
+        <v>2485831736500</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>분기 영업이익 100조 예상에도 불구하고 주가 부진. 노란봉투법 등 정치적 요인 및 자사주 매입에 대한 부정적 의견.</t>
+          <t>영업이익 100조에도 불구하고 주가 부진, 정치적 요인 및 자사주 매입에 대한 불만 제기. 하이닉스와의 비교 및 향후 하락 전망 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '자사주 매입', '노란봉투법']</t>
+          <t>['영업이익', '자사주 매입', '정치']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1784500</v>
+        <v>1782000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.07%</t>
+          <t>'-3.20%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="G15" t="n">
-        <v>1984</v>
+        <v>1950</v>
       </c>
       <c r="H15" t="n">
         <v>49.76</v>
@@ -1806,7 +1806,7 @@
         <v>49.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3306142980000</v>
+        <v>3411506584500</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재명 리스크, 오너 리스크, 정치적 악재 등으로 인한 주가 하락에 대한 부정적 전망.</t>
+          <t>이재명 리스크와 대통령실 관련 언급이 지배적이며, 주가 조작 의혹 및 오너 리스크 제기. 과거와 다른 하이닉스에 대한 부정적 평가.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['이재명 리스크', '오너 리스크', '주가 하락']</t>
+          <t>['이재명 리스크', '오너 리스크', '주가 조작']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261006_14.xlsx
+++ b/data/trending_integrated_20261006_14.xlsx
@@ -578,10 +578,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
         <v>242</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52848914990</v>
+        <v>52853286350</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -619,7 +619,7 @@
         <v>6000</v>
       </c>
       <c r="R2" t="n">
-        <v>553000</v>
+        <v>548000</v>
       </c>
       <c r="S2" t="n">
         <v>-34000</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7075</v>
+        <v>6990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+28.64%</t>
+          <t>'+27.09%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -702,7 +702,7 @@
         <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>110265535010</v>
+        <v>112757257315</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -711,10 +711,10 @@
         <v>3300</v>
       </c>
       <c r="R3" t="n">
-        <v>60000</v>
+        <v>-102000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17880</v>
+        <v>17850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.41%</t>
+          <t>'+16.21%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H4" t="n">
         <v>2.17</v>
@@ -794,7 +794,7 @@
         <v>1.37</v>
       </c>
       <c r="O4" t="n">
-        <v>104706575075</v>
+        <v>105186694480</v>
       </c>
       <c r="P4" t="n">
         <v>38400</v>
@@ -803,7 +803,7 @@
         <v>8010</v>
       </c>
       <c r="R4" t="n">
-        <v>-37000</v>
+        <v>-42000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46900</v>
+        <v>46750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.95%</t>
+          <t>'+15.57%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="F5" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="G5" t="n">
-        <v>4682</v>
+        <v>4778</v>
       </c>
       <c r="H5" t="n">
         <v>14.1</v>
@@ -886,7 +886,7 @@
         <v>14.11</v>
       </c>
       <c r="O5" t="n">
-        <v>248611245750</v>
+        <v>250343719275</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -895,10 +895,10 @@
         <v>24150</v>
       </c>
       <c r="R5" t="n">
-        <v>425000</v>
+        <v>474000</v>
       </c>
       <c r="S5" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4990</v>
+        <v>4995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.41%</t>
+          <t>'+13.52%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H6" t="n">
         <v>1.4</v>
@@ -978,7 +978,7 @@
         <v>1.02</v>
       </c>
       <c r="O6" t="n">
-        <v>137151862322</v>
+        <v>138260969552</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -987,10 +987,10 @@
         <v>592</v>
       </c>
       <c r="R6" t="n">
-        <v>2597000</v>
+        <v>3262000</v>
       </c>
       <c r="S6" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3130</v>
+        <v>3115</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.02%</t>
+          <t>'+9.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.57</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="H7" t="n">
         <v>1.82</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>51428050602</v>
+        <v>52201220112</v>
       </c>
       <c r="P7" t="n">
         <v>4810</v>
@@ -1079,7 +1079,7 @@
         <v>1400</v>
       </c>
       <c r="R7" t="n">
-        <v>35000</v>
+        <v>130000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20500</v>
+        <v>20450</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.10%</t>
+          <t>'+8.83%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.21</v>
       </c>
       <c r="E8" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
@@ -1162,7 +1162,7 @@
         <v>0.83</v>
       </c>
       <c r="O8" t="n">
-        <v>142594911290</v>
+        <v>143457398665</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1171,14 +1171,14 @@
         <v>6100</v>
       </c>
       <c r="R8" t="n">
-        <v>-73000</v>
+        <v>-58000</v>
       </c>
       <c r="S8" t="n">
         <v>2000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>은행권 보안 이슈와 연관된 보안주로서 연말 상승 기대감 표출. 긍정적 상승 징조 및 양자 보안 관련 언급.</t>
+          <t>은행권 해킹 이슈로 인한 보안주 부각, 엑스게이트의 상승 기대감과 실질적 주가 상승 확인.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', '양자 보안', '상승 기대']</t>
+          <t>['보안주', '양자 보안', '금융 고객사']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1447</v>
+        <v>1441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.99%</t>
+          <t>'+7.54%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H9" t="n">
         <v>1.09</v>
@@ -1254,7 +1254,7 @@
         <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>20082380898</v>
+        <v>20144914129</v>
       </c>
       <c r="P9" t="n">
         <v>2970</v>
@@ -1263,7 +1263,7 @@
         <v>890</v>
       </c>
       <c r="R9" t="n">
-        <v>-186000</v>
+        <v>-196000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18430</v>
+        <v>18550</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.54%</t>
+          <t>'+4.21%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="n">
         <v>79</v>
       </c>
       <c r="G10" t="n">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="H10" t="n">
         <v>3.81</v>
@@ -1346,7 +1346,7 @@
         <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>212210875780</v>
+        <v>217584616300</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1355,10 +1355,10 @@
         <v>1272</v>
       </c>
       <c r="R10" t="n">
-        <v>656000</v>
+        <v>599000</v>
       </c>
       <c r="S10" t="n">
-        <v>-9000</v>
+        <v>-10000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17660</v>
+        <v>17640</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.28%</t>
+          <t>'+0.17%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
         <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="H11" t="n">
         <v>9.390000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>58171706540</v>
+        <v>59155500740</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1447,10 +1447,10 @@
         <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>531000</v>
+        <v>569000</v>
       </c>
       <c r="S11" t="n">
-        <v>-136000</v>
+        <v>-155000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15360</v>
+        <v>15220</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'-0.85%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.14</v>
       </c>
       <c r="E12" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F12" t="n">
         <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H12" t="n">
         <v>0.32</v>
@@ -1530,7 +1530,7 @@
         <v>0.18</v>
       </c>
       <c r="O12" t="n">
-        <v>69713846510</v>
+        <v>70205514895</v>
       </c>
       <c r="P12" t="n">
         <v>29750</v>
@@ -1539,7 +1539,7 @@
         <v>12760</v>
       </c>
       <c r="R12" t="n">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19630</v>
+        <v>19620</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.65%</t>
+          <t>'-1.70%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F13" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="H13" t="n">
         <v>27.78</v>
@@ -1622,7 +1622,7 @@
         <v>27.73</v>
       </c>
       <c r="O13" t="n">
-        <v>37142476385</v>
+        <v>37795821955</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1631,10 +1631,10 @@
         <v>18440</v>
       </c>
       <c r="R13" t="n">
-        <v>-603000</v>
+        <v>-639000</v>
       </c>
       <c r="S13" t="n">
-        <v>-43000</v>
+        <v>-47000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G14" t="n">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="H14" t="n">
         <v>46.41</v>
@@ -1714,7 +1714,7 @@
         <v>46.41</v>
       </c>
       <c r="O14" t="n">
-        <v>2485831736500</v>
+        <v>2542298386500</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1723,14 +1723,14 @@
         <v>90200</v>
       </c>
       <c r="R14" t="n">
-        <v>-1259000</v>
+        <v>-1436000</v>
       </c>
       <c r="S14" t="n">
-        <v>374000</v>
+        <v>139000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>영업이익 100조에도 불구하고 주가 부진, 정치적 요인 및 자사주 매입에 대한 불만 제기. 하이닉스와의 비교 및 향후 하락 전망 언급.</t>
+          <t>분기 영업이익 100조 예상에도 주가 부진, 정치적 요인 및 자사주 매입 관련 불만 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '자사주 매입', '정치']</t>
+          <t>['영업이익', '자사주 매입', '반도체']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1782000</v>
+        <v>1780000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.20%</t>
+          <t>'-3.31%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="G15" t="n">
-        <v>1950</v>
+        <v>1928</v>
       </c>
       <c r="H15" t="n">
         <v>49.76</v>
@@ -1806,7 +1806,7 @@
         <v>49.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3411506584500</v>
+        <v>3526055429000</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1815,23 +1815,23 @@
         <v>403000</v>
       </c>
       <c r="R15" t="n">
-        <v>-549000</v>
+        <v>-648000</v>
       </c>
       <c r="S15" t="n">
-        <v>13000</v>
+        <v>-31000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재명 리스크와 대통령실 관련 언급이 지배적이며, 주가 조작 의혹 및 오너 리스크 제기. 과거와 다른 하이닉스에 대한 부정적 평가.</t>
+          <t>이재명 리스크와 오너십 문제로 인한 주가 하락에 대한 강한 불만과 정치적 책임론 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['이재명 리스크', '오너 리스크', '주가 조작']</t>
+          <t>['이재명 리스크', '오너십', '주가 조작']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261006_14.xlsx
+++ b/data/trending_integrated_20261006_14.xlsx
@@ -584,7 +584,7 @@
         <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52853286350</v>
+        <v>52858893660</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6990</v>
+        <v>7020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.09%</t>
+          <t>'+27.64%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -702,7 +702,7 @@
         <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>112757257315</v>
+        <v>114769828360</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17850</v>
+        <v>47200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.21%</t>
+          <t>'+16.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>78</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>428</v>
       </c>
       <c r="G4" t="n">
-        <v>95</v>
+        <v>4653</v>
       </c>
       <c r="H4" t="n">
-        <v>2.17</v>
+        <v>14.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15360</v>
+        <v>40450</v>
       </c>
       <c r="K4" t="n">
-        <v>18000</v>
+        <v>42700</v>
       </c>
       <c r="L4" t="n">
-        <v>18640</v>
+        <v>50700</v>
       </c>
       <c r="M4" t="n">
-        <v>16800</v>
+        <v>42150</v>
       </c>
       <c r="N4" t="n">
-        <v>1.37</v>
+        <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>105186694480</v>
+        <v>252048856275</v>
       </c>
       <c r="P4" t="n">
-        <v>38400</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>8010</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>-42000</v>
+        <v>474000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
+          <t>HLB, FDA 승인 기대감 및 허가 관련 뉴스 기반 주가 급등 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '테마']</t>
+          <t>['FDA', '승인', '간암 신약']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>488280</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46750</v>
+        <v>17740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.57%</t>
+          <t>'+15.49%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="n">
-        <v>799</v>
+        <v>78</v>
       </c>
       <c r="F5" t="n">
-        <v>428</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>4778</v>
+        <v>95</v>
       </c>
       <c r="H5" t="n">
-        <v>14.1</v>
+        <v>2.17</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>40450</v>
+        <v>15360</v>
       </c>
       <c r="K5" t="n">
-        <v>42700</v>
+        <v>18000</v>
       </c>
       <c r="L5" t="n">
-        <v>50700</v>
+        <v>18640</v>
       </c>
       <c r="M5" t="n">
-        <v>42150</v>
+        <v>16800</v>
       </c>
       <c r="N5" t="n">
-        <v>14.11</v>
+        <v>1.37</v>
       </c>
       <c r="O5" t="n">
-        <v>250343719275</v>
+        <v>105695433985</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>38400</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>8010</v>
       </c>
       <c r="R5" t="n">
-        <v>474000</v>
+        <v>-42000</v>
       </c>
       <c r="S5" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>리보세라닙의 FDA 실사 결과 VAI 획득 및 간암 신약 FDA 승인 기대감으로 인한 주가 상승 전망.</t>
+          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['리보세라닙', 'FDA 승인', '간암 신약']</t>
+          <t>['AI 보안', '대장주', '테마']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,12 +919,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>488280</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4995</v>
+        <v>5050</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.52%</t>
+          <t>'+14.77%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H6" t="n">
         <v>1.4</v>
@@ -978,7 +978,7 @@
         <v>1.02</v>
       </c>
       <c r="O6" t="n">
-        <v>138260969552</v>
+        <v>140914373167</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3115</v>
+        <v>3130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.49%</t>
+          <t>'+10.02%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.57</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
         <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H7" t="n">
         <v>1.82</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>52201220112</v>
+        <v>52732321892</v>
       </c>
       <c r="P7" t="n">
         <v>4810</v>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20450</v>
+        <v>20550</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.83%</t>
+          <t>'+9.37%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.21</v>
       </c>
       <c r="E8" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F8" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G8" t="n">
         <v>214</v>
@@ -1162,7 +1162,7 @@
         <v>0.83</v>
       </c>
       <c r="O8" t="n">
-        <v>143457398665</v>
+        <v>144026224290</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.54%</t>
+          <t>'+7.61%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.17</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H9" t="n">
         <v>1.09</v>
@@ -1254,7 +1254,7 @@
         <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>20144914129</v>
+        <v>20338394217</v>
       </c>
       <c r="P9" t="n">
         <v>2970</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18550</v>
+        <v>18540</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.21%</t>
+          <t>'+4.16%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F10" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="H10" t="n">
         <v>3.81</v>
@@ -1346,7 +1346,7 @@
         <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>217584616300</v>
+        <v>223888507195</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1412,7 +1412,7 @@
         <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="H11" t="n">
         <v>9.390000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>59155500740</v>
+        <v>59998988440</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1447,7 +1447,7 @@
         <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>569000</v>
+        <v>572000</v>
       </c>
       <c r="S11" t="n">
         <v>-155000</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15220</v>
+        <v>15260</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.85%</t>
+          <t>'-0.59%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.14</v>
       </c>
       <c r="E12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F12" t="n">
         <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H12" t="n">
         <v>0.32</v>
@@ -1530,7 +1530,7 @@
         <v>0.18</v>
       </c>
       <c r="O12" t="n">
-        <v>70205514895</v>
+        <v>70869481190</v>
       </c>
       <c r="P12" t="n">
         <v>29750</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집에 대한 의문 제기 및 초저평가 논의. 주가 상승에 대한 기대와 함께 단기적인 움직임에 대한 관망세.</t>
+          <t>기타법인 자사주 매집에 따른 주가 상승 기대감 있으나, 구체적인 호재는 부족.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주 매집', '초저평가', '수급']</t>
+          <t>['자사주', '매집', '주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19620</v>
+        <v>272000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.45%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>105</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>68</v>
+        <v>449</v>
       </c>
       <c r="G13" t="n">
-        <v>309</v>
+        <v>1587</v>
       </c>
       <c r="H13" t="n">
-        <v>27.78</v>
+        <v>46.41</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>19960</v>
+        <v>276000</v>
       </c>
       <c r="K13" t="n">
-        <v>20150</v>
+        <v>278500</v>
       </c>
       <c r="L13" t="n">
-        <v>20150</v>
+        <v>279000</v>
       </c>
       <c r="M13" t="n">
-        <v>19600</v>
+        <v>270000</v>
       </c>
       <c r="N13" t="n">
-        <v>27.73</v>
+        <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>37795821955</v>
+        <v>2647797299000</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>18440</v>
+        <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>-639000</v>
+        <v>-1469000</v>
       </c>
       <c r="S13" t="n">
-        <v>-47000</v>
+        <v>139000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>수주 기대감에도 불구하고 주가 부진에 대한 답답함과 불신 드러남.</t>
+          <t>100조 영업이익 기대에도 불구하고 주가 부진, 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '조선주', '주가']</t>
+          <t>['영업이익', '주가', '정치']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>271000</v>
+        <v>19610</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.81%</t>
+          <t>'-1.75%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>108</v>
       </c>
       <c r="F14" t="n">
-        <v>450</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>1529</v>
+        <v>314</v>
       </c>
       <c r="H14" t="n">
-        <v>46.41</v>
+        <v>27.78</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>276000</v>
+        <v>19960</v>
       </c>
       <c r="K14" t="n">
-        <v>278500</v>
+        <v>20150</v>
       </c>
       <c r="L14" t="n">
-        <v>279000</v>
+        <v>20150</v>
       </c>
       <c r="M14" t="n">
-        <v>270000</v>
+        <v>19600</v>
       </c>
       <c r="N14" t="n">
-        <v>46.41</v>
+        <v>27.73</v>
       </c>
       <c r="O14" t="n">
-        <v>2542298386500</v>
+        <v>38072889475</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>90200</v>
+        <v>18440</v>
       </c>
       <c r="R14" t="n">
-        <v>-1436000</v>
+        <v>-642000</v>
       </c>
       <c r="S14" t="n">
-        <v>139000</v>
+        <v>-47000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>분기 영업이익 100조 예상에도 주가 부진, 정치적 요인 및 자사주 매입 관련 불만 제기.</t>
+          <t>수주 기대감에도 불구하고 주가 부진에 대한 답답함과 불신 드러남.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '자사주 매입', '반도체']</t>
+          <t>['수주', '조선주', '주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1780000</v>
+        <v>1778000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.31%</t>
+          <t>'-3.42%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1780,7 +1780,7 @@
         <v>463</v>
       </c>
       <c r="G15" t="n">
-        <v>1928</v>
+        <v>1924</v>
       </c>
       <c r="H15" t="n">
         <v>49.76</v>
@@ -1806,7 +1806,7 @@
         <v>49.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3526055429000</v>
+        <v>3630039859500</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1815,14 +1815,14 @@
         <v>403000</v>
       </c>
       <c r="R15" t="n">
-        <v>-648000</v>
+        <v>-658000</v>
       </c>
       <c r="S15" t="n">
         <v>-31000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재명 리스크와 오너십 문제로 인한 주가 하락에 대한 강한 불만과 정치적 책임론 제기.</t>
+          <t>정치적 리스크와 오너 리스크로 인한 주가 하락 및 부정적 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['이재명 리스크', '오너십', '주가 조작']</t>
+          <t>['정치', '리스크', '주가']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261006_14.xlsx
+++ b/data/trending_integrated_20261006_14.xlsx
@@ -584,7 +584,7 @@
         <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52858893660</v>
+        <v>52876392110</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7020</v>
+        <v>6980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.64%</t>
+          <t>'+26.91%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -702,7 +702,7 @@
         <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>114769828360</v>
+        <v>116452633840</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47200</v>
+        <v>47550</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.69%</t>
+          <t>'+17.55%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>428</v>
       </c>
       <c r="G4" t="n">
-        <v>4653</v>
+        <v>4468</v>
       </c>
       <c r="H4" t="n">
         <v>14.1</v>
@@ -794,7 +794,7 @@
         <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>252048856275</v>
+        <v>254579627000</v>
       </c>
       <c r="P4" t="n">
         <v>69200</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HLB, FDA 승인 기대감 및 허가 관련 뉴스 기반 주가 급등 전망.</t>
+          <t>리보세라닙 관련 FDA 실사 결과(VAI) 긍정적. 간암 신약 승인 기대감 고조 및 로슈 능가 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['FDA', '승인', '간암 신약']</t>
+          <t>['리보세라닙', 'FDA 실사', '간암 신약']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17740</v>
+        <v>5090</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.49%</t>
+          <t>'+15.68%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="H5" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>15360</v>
+        <v>4400</v>
       </c>
       <c r="K5" t="n">
-        <v>18000</v>
+        <v>4435</v>
       </c>
       <c r="L5" t="n">
-        <v>18640</v>
+        <v>5130</v>
       </c>
       <c r="M5" t="n">
-        <v>16800</v>
+        <v>4305</v>
       </c>
       <c r="N5" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>105695433985</v>
+        <v>145793844832</v>
       </c>
       <c r="P5" t="n">
-        <v>38400</v>
+        <v>8100</v>
       </c>
       <c r="Q5" t="n">
-        <v>8010</v>
+        <v>592</v>
       </c>
       <c r="R5" t="n">
-        <v>-42000</v>
+        <v>3262000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
+          <t>해외 반도체 기업 급등에 따른 연동 기대감. 외국인 매수세 집중 및 상한가 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '테마']</t>
+          <t>['외국인매수', '상한가', '반도체']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>488280</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5050</v>
+        <v>17660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+14.77%</t>
+          <t>'+14.97%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4</v>
+        <v>2.17</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>4400</v>
+        <v>15360</v>
       </c>
       <c r="K6" t="n">
-        <v>4435</v>
+        <v>18000</v>
       </c>
       <c r="L6" t="n">
-        <v>5130</v>
+        <v>18640</v>
       </c>
       <c r="M6" t="n">
-        <v>4305</v>
+        <v>16800</v>
       </c>
       <c r="N6" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="O6" t="n">
-        <v>140914373167</v>
+        <v>106266422115</v>
       </c>
       <c r="P6" t="n">
-        <v>8100</v>
+        <v>38400</v>
       </c>
       <c r="Q6" t="n">
-        <v>592</v>
+        <v>8010</v>
       </c>
       <c r="R6" t="n">
-        <v>3262000</v>
+        <v>-42000</v>
       </c>
       <c r="S6" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>해외 반도체 기업 급등에 따른 연동 기대감. 외국인 매수세 집중 및 상한가 기대.</t>
+          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인매수', '상한가', '반도체']</t>
+          <t>['AI 보안', '대장주', '테마']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>488280</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3130</v>
+        <v>3120</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.02%</t>
+          <t>'+9.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H7" t="n">
         <v>1.82</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>52732321892</v>
+        <v>52945335776</v>
       </c>
       <c r="P7" t="n">
         <v>4810</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20550</v>
+        <v>20500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.37%</t>
+          <t>'+9.10%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.21</v>
       </c>
       <c r="E8" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F8" t="n">
         <v>82</v>
       </c>
       <c r="G8" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
@@ -1162,7 +1162,7 @@
         <v>0.83</v>
       </c>
       <c r="O8" t="n">
-        <v>144026224290</v>
+        <v>144459938165</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>은행권 해킹 이슈로 인한 보안주 부각, 엑스게이트의 상승 기대감과 실질적 주가 상승 확인.</t>
+          <t>금융권 보안 위협에 따른 보안주 부각. 금융 고객사 다수 확보 및 양자 보안 기술 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', '양자 보안', '금융 고객사']</t>
+          <t>['보안주', '양자 보안', '금융 보안']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1442</v>
+        <v>1447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.61%</t>
+          <t>'+7.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.17</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H9" t="n">
         <v>1.09</v>
@@ -1254,7 +1254,7 @@
         <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>20338394217</v>
+        <v>20393444105</v>
       </c>
       <c r="P9" t="n">
         <v>2970</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18540</v>
+        <v>18520</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.16%</t>
+          <t>'+4.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G10" t="n">
-        <v>810</v>
+        <v>853</v>
       </c>
       <c r="H10" t="n">
         <v>3.81</v>
@@ -1346,7 +1346,7 @@
         <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>223888507195</v>
+        <v>226067299420</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 광통신 섹터 강세 및 3분기 영업이익 개선. 전고점 돌파 및 매물 소화 과정 분석.</t>
+          <t>미국 증시 광통신 섹터 강세 및 국내 3분기 영업이익 증가. 전고점 돌파 및 매물 소화 과정 분석.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '매물대']</t>
+          <t>['광통신', '영업이익', '전고점']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17640</v>
+        <v>17670</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.17%</t>
+          <t>'+0.34%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
         <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H11" t="n">
         <v>9.390000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>59998988440</v>
+        <v>60843371845</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15260</v>
+        <v>15220</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'-0.85%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.14</v>
       </c>
       <c r="E12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F12" t="n">
         <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H12" t="n">
         <v>0.32</v>
@@ -1530,7 +1530,7 @@
         <v>0.18</v>
       </c>
       <c r="O12" t="n">
-        <v>70869481190</v>
+        <v>71284829090</v>
       </c>
       <c r="P12" t="n">
         <v>29750</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>272000</v>
+        <v>271500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.45%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G13" t="n">
-        <v>1587</v>
+        <v>1571</v>
       </c>
       <c r="H13" t="n">
         <v>46.41</v>
@@ -1622,7 +1622,7 @@
         <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>2647797299000</v>
+        <v>2687182200750</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>100조 영업이익 기대에도 불구하고 주가 부진, 정치적 이슈 언급.</t>
+          <t>분기 영업이익 100조 예상에도 불구하고 주가 부진. 정치적 요인 및 자사주 매입 관련 불만 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '주가', '정치']</t>
+          <t>['영업이익', '자사주 매입', '주가 부진']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,10 +1682,10 @@
         <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G14" t="n">
         <v>314</v>
@@ -1714,7 +1714,7 @@
         <v>27.73</v>
       </c>
       <c r="O14" t="n">
-        <v>38072889475</v>
+        <v>38500595075</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1778000</v>
+        <v>1776000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.42%</t>
+          <t>'-3.53%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="G15" t="n">
-        <v>1924</v>
+        <v>1981</v>
       </c>
       <c r="H15" t="n">
         <v>49.76</v>
@@ -1806,7 +1806,7 @@
         <v>49.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3630039859500</v>
+        <v>3734538685000</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 리스크와 오너 리스크로 인한 주가 하락 및 부정적 전망.</t>
+          <t>정치적 리스크 및 오너십 문제로 인한 주가 하락 우려. 과거 고점 대비 비정상적 폭등 지적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['정치', '리스크', '주가']</t>
+          <t>['정치 리스크', '오너십', '주가 조작']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261006_14.xlsx
+++ b/data/trending_integrated_20261006_14.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52876392110</v>
+        <v>52894059690</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -670,13 +670,13 @@
         <v>0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F3" t="n">
         <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -702,7 +702,7 @@
         <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>116452633840</v>
+        <v>117720616425</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>우리은행 해킹 방어 관련 티오리 협력 언급. 3분기 흑자 전환 및 보안주 동반 상승 기대.</t>
+          <t>양자암호, 보안 기업으로서의 잠재력 언급. 해킹 방어 및 우리은행 협력 사례 제시. 단기 변동성에 대한 의견도 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', '양자암호', '흑자']</t>
+          <t>['양자암호', '해킹 방어', '보안']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47550</v>
+        <v>47250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.55%</t>
+          <t>'+16.81%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="G4" t="n">
-        <v>4468</v>
+        <v>4530</v>
       </c>
       <c r="H4" t="n">
         <v>14.1</v>
@@ -794,7 +794,7 @@
         <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>254579627000</v>
+        <v>256081379900</v>
       </c>
       <c r="P4" t="n">
         <v>69200</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5090</v>
+        <v>5045</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.68%</t>
+          <t>'+14.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>71</v>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>145793844832</v>
+        <v>149069573927</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17660</v>
+        <v>17590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+14.97%</t>
+          <t>'+14.52%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.8</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
         <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H6" t="n">
         <v>2.17</v>
@@ -978,7 +978,7 @@
         <v>1.37</v>
       </c>
       <c r="O6" t="n">
-        <v>106266422115</v>
+        <v>106838576900</v>
       </c>
       <c r="P6" t="n">
         <v>38400</v>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3120</v>
+        <v>3095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.67%</t>
+          <t>'+8.79%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.57</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
         <v>179</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>52945335776</v>
+        <v>53465080001</v>
       </c>
       <c r="P7" t="n">
         <v>4810</v>
@@ -1115,184 +1115,184 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20500</v>
+        <v>1453</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.10%</t>
+          <t>'+8.43%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18790</v>
+        <v>1340</v>
       </c>
       <c r="K8" t="n">
-        <v>21400</v>
+        <v>1370</v>
       </c>
       <c r="L8" t="n">
-        <v>22300</v>
+        <v>1555</v>
       </c>
       <c r="M8" t="n">
-        <v>20050</v>
+        <v>1360</v>
       </c>
       <c r="N8" t="n">
-        <v>0.83</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>144459938165</v>
+        <v>20472652536</v>
       </c>
       <c r="P8" t="n">
-        <v>30550</v>
+        <v>2970</v>
       </c>
       <c r="Q8" t="n">
-        <v>6100</v>
+        <v>890</v>
       </c>
       <c r="R8" t="n">
-        <v>-58000</v>
+        <v>-196000</v>
       </c>
       <c r="S8" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>금융권 보안 위협에 따른 보안주 부각. 금융 고객사 다수 확보 및 양자 보안 기술 기대감.</t>
+          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', '양자 보안', '금융 보안']</t>
+          <t>['LNG', '송유관', '테마']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1447</v>
+        <v>20300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.99%</t>
+          <t>'+8.04%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="H9" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1340</v>
+        <v>18790</v>
       </c>
       <c r="K9" t="n">
-        <v>1370</v>
+        <v>21400</v>
       </c>
       <c r="L9" t="n">
-        <v>1555</v>
+        <v>22300</v>
       </c>
       <c r="M9" t="n">
-        <v>1360</v>
+        <v>20050</v>
       </c>
       <c r="N9" t="n">
-        <v>1.26</v>
+        <v>0.83</v>
       </c>
       <c r="O9" t="n">
-        <v>20393444105</v>
+        <v>145189467415</v>
       </c>
       <c r="P9" t="n">
-        <v>2970</v>
+        <v>30550</v>
       </c>
       <c r="Q9" t="n">
-        <v>890</v>
+        <v>6100</v>
       </c>
       <c r="R9" t="n">
-        <v>-196000</v>
+        <v>-58000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
+          <t>은행 해킹 사태와 연관된 보안주로서의 상승 기대감. 금융 고객사 확보 및 경쟁사 동반 상승 가능성 언급. 목표가 및 매물대에 대한 의견도 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['LNG', '송유관', '테마']</t>
+          <t>['보안주', '금융 고객사', '상승 기대감']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18520</v>
+        <v>18530</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.04%</t>
+          <t>'+4.10%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" t="n">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="H10" t="n">
         <v>3.81</v>
@@ -1346,7 +1346,7 @@
         <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>226067299420</v>
+        <v>229016002220</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17670</v>
+        <v>17680</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.34%</t>
+          <t>'+0.40%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H11" t="n">
         <v>9.390000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>60843371845</v>
+        <v>61842723995</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15220</v>
+        <v>272000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.85%</t>
+          <t>'-1.45%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>134</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>450</v>
       </c>
       <c r="G12" t="n">
-        <v>401</v>
+        <v>1588</v>
       </c>
       <c r="H12" t="n">
-        <v>0.32</v>
+        <v>46.41</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>15350</v>
+        <v>276000</v>
       </c>
       <c r="K12" t="n">
-        <v>14920</v>
+        <v>278500</v>
       </c>
       <c r="L12" t="n">
-        <v>16590</v>
+        <v>279000</v>
       </c>
       <c r="M12" t="n">
-        <v>14300</v>
+        <v>270000</v>
       </c>
       <c r="N12" t="n">
-        <v>0.18</v>
+        <v>46.41</v>
       </c>
       <c r="O12" t="n">
-        <v>71284829090</v>
+        <v>2782361216000</v>
       </c>
       <c r="P12" t="n">
-        <v>29750</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>12760</v>
+        <v>90200</v>
       </c>
       <c r="R12" t="n">
-        <v>12000</v>
+        <v>-1469000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>139000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집에 따른 주가 상승 기대감 있으나, 구체적인 호재는 부족.</t>
+          <t>분기 영업이익 100조 예상에도 불구하고 주가 부진, 노란봉투법 등 정치적 요인 언급. 자사주 매입 관련 부정적 의견.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주', '매집', '주가']</t>
+          <t>['영업이익', '자사주 매입', '주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>271500</v>
+        <v>19630</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.65%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>111</v>
       </c>
       <c r="F13" t="n">
-        <v>451</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
-        <v>1571</v>
+        <v>316</v>
       </c>
       <c r="H13" t="n">
-        <v>46.41</v>
+        <v>27.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,152 +1607,152 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>276000</v>
+        <v>19960</v>
       </c>
       <c r="K13" t="n">
-        <v>278500</v>
+        <v>20150</v>
       </c>
       <c r="L13" t="n">
-        <v>279000</v>
+        <v>20150</v>
       </c>
       <c r="M13" t="n">
-        <v>270000</v>
+        <v>19600</v>
       </c>
       <c r="N13" t="n">
-        <v>46.41</v>
+        <v>27.73</v>
       </c>
       <c r="O13" t="n">
-        <v>2687182200750</v>
+        <v>40318281350</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>90200</v>
+        <v>18440</v>
       </c>
       <c r="R13" t="n">
-        <v>-1469000</v>
+        <v>-642000</v>
       </c>
       <c r="S13" t="n">
-        <v>139000</v>
+        <v>-47000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>분기 영업이익 100조 예상에도 불구하고 주가 부진. 정치적 요인 및 자사주 매입 관련 불만 제기.</t>
+          <t>수주 기대감에도 불구하고 주가 부진에 대한 답답함과 불신 드러남.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '자사주 매입', '주가 부진']</t>
+          <t>['수주', '조선주', '주가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19610</v>
+        <v>14970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.75%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="E14" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="F14" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>314</v>
+        <v>408</v>
       </c>
       <c r="H14" t="n">
-        <v>27.78</v>
+        <v>0.32</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19960</v>
+        <v>15350</v>
       </c>
       <c r="K14" t="n">
-        <v>20150</v>
+        <v>14920</v>
       </c>
       <c r="L14" t="n">
-        <v>20150</v>
+        <v>16590</v>
       </c>
       <c r="M14" t="n">
-        <v>19600</v>
+        <v>14300</v>
       </c>
       <c r="N14" t="n">
-        <v>27.73</v>
+        <v>0.18</v>
       </c>
       <c r="O14" t="n">
-        <v>38500595075</v>
+        <v>72443386495</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>29750</v>
       </c>
       <c r="Q14" t="n">
-        <v>18440</v>
+        <v>12760</v>
       </c>
       <c r="R14" t="n">
-        <v>-642000</v>
+        <v>12000</v>
       </c>
       <c r="S14" t="n">
-        <v>-47000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>수주 기대감에도 불구하고 주가 부진에 대한 답답함과 불신 드러남.</t>
+          <t>기타법인 자사주 매집에 따른 주가 상승 기대감 있으나, 구체적인 호재는 부족.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수주', '조선주', '주가']</t>
+          <t>['자사주', '매집', '주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1776000</v>
+        <v>1779000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'-3.37%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="G15" t="n">
-        <v>1981</v>
+        <v>2023</v>
       </c>
       <c r="H15" t="n">
         <v>49.76</v>
@@ -1806,7 +1806,7 @@
         <v>49.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3734538685000</v>
+        <v>3845298106000</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 리스크 및 오너십 문제로 인한 주가 하락 우려. 과거 고점 대비 비정상적 폭등 지적.</t>
+          <t>이재명 리스크, 대통령실 정책 비판 등 정치적 요인으로 인한 주가 하락 언급. 오너 경영 방식 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['정치 리스크', '오너십', '주가 조작']</t>
+          <t>['이재명 리스크', '주가 조작', '오너 경영']</t>
         </is>
       </c>
       <c r="X15" t="n">
